--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ_ΕΒΔΟΜΑΔΙΑΙΑ/2026-W13/XLSX/ΕΒΔΟΜΑΔΙΑΙΟ_ΣΗΜΕΙΩΜΑ_ΣΗΘΥΑ_ΘΕΣΣΑΛΟΝΙΚΗΣ_2_ΜΟΝΟΠΡΟΣΩΠΗ_ΙΚΕ_2026-W13.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ_ΕΒΔΟΜΑΔΙΑΙΑ/2026-W13/XLSX/ΕΒΔΟΜΑΔΙΑΙΟ_ΣΗΜΕΙΩΜΑ_ΣΗΘΥΑ_ΘΕΣΣΑΛΟΝΙΚΗΣ_2_ΜΟΝΟΠΡΟΣΩΠΗ_ΙΚΕ_2026-W13.xlsx
@@ -2816,7 +2816,11 @@
       <c r="M5" s="1" t="n"/>
     </row>
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="11">
-      <c r="B6" s="83" t="n"/>
+      <c r="B6" s="83" t="inlineStr">
+        <is>
+          <t>03/04/26</t>
+        </is>
+      </c>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="84" t="inlineStr">
         <is>
